--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,21 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G-NG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,6 +488,21 @@
       </c>
       <c r="C4" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G-SET3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,21 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-140G-SET3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-140G</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,6 +520,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-180G-SET3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-180G</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-280G-SET3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-280G</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-380G-SET3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-280G</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,22 +523,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G-SET3</t>
+          <t>HFF02001-SK-280G-SET3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G</t>
+          <t>HFF02001-SK-280G</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-280G-SET3</t>
+          <t>HFF02001-SK-380G-SET3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,21 +547,6 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HFF02001-SK-380G-SET3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HFF02001-SK-280G</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-180G-SET3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-180G</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -493,12 +493,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G-SET3</t>
+          <t>HFF02001-BK-140G-SET3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G</t>
+          <t>HFF02001-BK-140G</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -508,12 +508,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G-SET3</t>
+          <t>HFF02001-SK-280G-SET3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G</t>
+          <t>HFF02001-SK-280G</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFF02001-SK-280G-SET3</t>
+          <t>HFF02001-SK-380G-SET3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,12 +538,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-380G-SET3</t>
+          <t>HFF02001-SK-180G-SET3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-280G</t>
+          <t>HFF02001-SK-180G</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -553,16 +553,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G-SET3</t>
+          <t>HFF02001-SK-140G-SET3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G</t>
+          <t>HFF02001-SK-140G</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -493,12 +493,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G-SET3</t>
+          <t>HFF02001-SK-280G-SET3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G</t>
+          <t>HFF02001-SK-280G</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -508,7 +508,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HFF02001-SK-280G-SET3</t>
+          <t>HFF02001-SK-380G-SET3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFF02001-SK-380G-SET3</t>
+          <t>HFF02001-SK-180G-SET3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HFF02001-SK-280G</t>
+          <t>HFF02001-SK-180G</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -538,31 +538,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G-SET3</t>
+          <t>HFF02001-SK-140G-SET3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G</t>
+          <t>HFF02001-SK-140G</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G-SET3</t>
+          <t>HFF02001-BK-140G-SET3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G</t>
+          <t>HFF02001-BK-140G</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,30 +538,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G-SET3</t>
+          <t>HFF02001-BK-140G-SET3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G</t>
+          <t>HFF02001-BK-140G</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HFF02001-BK-140G-SET3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HFF02001-BK-140G</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G-SET3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -523,12 +523,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G-SET3</t>
+          <t>HFF02001-BK-140G-SET3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G</t>
+          <t>HFF02001-BK-140G</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -538,12 +538,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G-SET3</t>
+          <t>HFF02001-SK-140G-SET3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G</t>
+          <t>HFF02001-SK-140G</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -553,12 +553,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G-SET3</t>
+          <t>HFF02001-SK-180G-SET3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G</t>
+          <t>HFF02001-SK-180G</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-180G-SET3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-180G</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,12 +508,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HFF02001-SK-380G-SET3</t>
+          <t>HFF02001-BK-140G-SET3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HFF02001-SK-280G</t>
+          <t>HFF02001-BK-140G</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -523,12 +523,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G-SET3</t>
+          <t>HFF02001-SK-140G-SET3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HFF02001-BK-140G</t>
+          <t>HFF02001-SK-140G</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -538,12 +538,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G-SET3</t>
+          <t>HFF02001-SK-180G-SET3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HFF02001-SK-140G</t>
+          <t>HFF02001-SK-180G</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -553,30 +553,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G-SET3</t>
+          <t>HFF02001-BK-180G-SET3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HFF02001-SK-180G</t>
+          <t>HFF02001-BK-180G</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HFF02001-BK-180G-SET3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HFF02001-BK-180G</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-380G-SET3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-380G</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-380G-SET3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-380G</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,6 +595,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-280G-SET3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HFF02001-BK-280G</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,6 +610,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-180G-NG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-180G</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-280G-NG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-280G</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,21 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>組合貨號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>原料貨號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>原料數量</t>
         </is>
@@ -637,6 +625,36 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>YGK03002-OR30-PK-DIY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>YGJ03002-OR</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>YGK03002-OR30-PK-DIY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>YGK03002-PK</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-RR-DIY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>YGJ03002-OR</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-RR-DIY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>YGK03002-RR</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-CG-ASSY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-CG-ASSY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>YGK03002-CG</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,12 +661,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>YGK03002-OG30-RR-DIY</t>
+          <t>YGK03002-OG30-CG-ASSY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YGJ03002-OR</t>
+          <t>YGJ03002-OG</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,45 +676,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>YGK03002-OG30-RR-DIY</t>
+          <t>YGK03002-OG30-CG-ASSY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YGK03002-RR</t>
+          <t>YGK03002-CG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>YGK03002-OG30-CG-ASSY</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>YGJ03002-OG</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>YGK03002-OG30-CG-ASSY</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>YGK03002-CG</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-RR-DIY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-RR-DIY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>YGK03002-RR</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,6 +718,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-CG-DIY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>YGK03002-OG30-CG-DIY</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>YGK03002-CG</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,6 +748,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG-SET30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,6 +805,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>YGK03002-RR-ASSY</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>YGK03002-RR</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/組合貨號.xlsx
+++ b/data/組合貨號.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,6 +820,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>YGK03002-RR-DIY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>YGK03002-RR</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
